--- a/results/pathways/BC_vs_PC/mcg_modularanalysis_BC_vs_PC.xlsx
+++ b/results/pathways/BC_vs_PC/mcg_modularanalysis_BC_vs_PC.xlsx
@@ -37,10 +37,10 @@
     <t>module_1</t>
   </si>
   <si>
-    <t>Demethylcitalopram$3,4-Dihydroxymandelate$Indole-3-acetaldehyde$3-Carbamoyl-2-phenylpropionic acid$3-Methoxy-4-hydroxyphenylglycolaldehyde$3-Methoxytyramine$L-Tyrosine$$Dopamine 3-O-sulfate$L-Tryptophan$3,4-Dihydroxymandelaldehyde$L-Metanephrine$5-Hydroxykynurenamine$3-Carbamoyl-2-phenylpropionaldehyde$$Dopaquinone$Formylkynurenine$L-Kynurenine$Homogentisate$Formyl-N-acetyl-5-methoxykynurenamine$5-Hydroxy-L-tryptophan$adrenochrome$L-Formylkynurenine$$Dopamine$L-Phenylalanine$Didemethylcitalopram$Serotonin$D-Tryptophan$$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$Formyl-5-hydroxykynurenamine$N-Methylserotonin$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$2-Hydroxy-3-(4-hydroxyphenyl)propenoate; 4-Hydroxy-enol-phenylpyruvate$4-(2-Aminophenyl)-2,4-dioxobutanoate$Phenylpyruvate$Epinine; Deoxyepinephrine$5-Phenyl-1,3-oxazinane-2,4-dione$6-Hydroxymelatonin$enol-Phenylpyruvate$2-Phenyl-1,3-propanediol monocarbamate$3-(4-Hydroxyphenyl)pyruvate$3,4-Dihydroxy-L-phenylalanine$3-O-methyldopa$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$Melatonin; N-Acetyl-5-methoxytryptamine$2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$3-Methoxy-4-hydroxymandelate; Vanillylmandelic acid$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$L-Normetanephrine</t>
-  </si>
-  <si>
-    <t>C16608,C05580,C00637,C16591,C05583,C05587,C00082,CE2173,C13690,C00078,C05577,C05588,C05638,C16587,CE2172,C00822,C02406,C00328,C00544,C05642,C00643,CE5536,C02700,CE5860,C03758,C00079,C16609,C00780,C00525,CE3140,C00788,C05647,C06212,C09642,C05350,C01252,C00166,C07453,C16596,C05643,C02763,C16586,C01179,C00355,CE2176,C16595,C01598,C05604,C05584,C00978,C05589</t>
+    <t>5-Phenyl-1,3-oxazinane-2,4-dione$D-Tryptophan$Didemethylcitalopram$4-(2-Aminophenyl)-2,4-dioxobutanoate$3,4-Dihydroxymandelaldehyde$L-Metanephrine$Demethylcitalopram$L-Formylkynurenine$L-Tyrosine$Serotonin$$3-(4-Hydroxyphenyl)pyruvate$Epinine; Deoxyepinephrine$3-O-methyldopa$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$2-Phenyl-1,3-propanediol monocarbamate$3-Methoxy-4-hydroxyphenylglycolaldehyde$L-Tryptophan$Phenylpyruvate$2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Kynurenine$Dopamine$L-Normetanephrine$L-Phenylalanine$5-Hydroxykynurenamine$Homogentisate$Melatonin; N-Acetyl-5-methoxytryptamine$$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$2-Hydroxy-3-(4-hydroxyphenyl)propenoate; 4-Hydroxy-enol-phenylpyruvate$$Dopaquinone$3-Methoxy-4-hydroxymandelate; Vanillylmandelic acid$3-Carbamoyl-2-phenylpropionaldehyde$Formyl-5-hydroxykynurenamine$adrenochrome$3-Methoxytyramine$Formyl-N-acetyl-5-methoxykynurenamine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$Indole-3-acetaldehyde$3-Carbamoyl-2-phenylpropionic acid$6-Hydroxymelatonin$Formylkynurenine$enol-Phenylpyruvate$N-Methylserotonin$3,4-Dihydroxymandelate$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$3,4-Dihydroxy-L-phenylalanine$Dopamine 3-O-sulfate$5-Hydroxy-L-tryptophan</t>
+  </si>
+  <si>
+    <t>C16596,C00525,C16609,C01252,C05577,C05588,C16608,C02700,C00082,C00780,CE5860,C01179,C07453,CE2176,C09642,C16586,C05583,C00078,C00166,C05604,C00328,C03758,C05589,C00079,C05638,C00544,C01598,CE3140,C16595,C05350,CE2172,C00822,C05584,C16587,C05647,CE5536,C05587,C05642,C00788,CE2173,C00637,C16591,C05643,C02406,C02763,C06212,C05580,C00978,C00355,C13690,C00643</t>
   </si>
   <si>
     <t>(26, 'Tyrosine metabolism');(18, 'Tryptophan metabolism');(7, 'Drug metabolism - cytochrome P450')</t>
@@ -49,10 +49,10 @@
     <t>module_2</t>
   </si>
   <si>
-    <t>Demethylcitalopram$3,4-Dihydroxymandelate$Indole-3-acetaldehyde$3-Methoxy-4-hydroxyphenylglycolaldehyde$3-Methoxytyramine$$3,4-Dihydroxymandelaldehyde$L-Metanephrine$5-Hydroxykynurenamine$$adrenochrome$Didemethylcitalopram$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$Epinine; Deoxyepinephrine$Dopamine$3-Methoxy-4-hydroxymandelate; Vanillylmandelic acid$Dopamine 3-O-sulfate$L-Normetanephrine</t>
-  </si>
-  <si>
-    <t>C16608,C05580,C00637,C05583,C05587,CE2173,C05577,C05588,C05638,CE2172,CE5536,C16609,C00788,C09642,C07453,C03758,C05584,C13690,C05589</t>
+    <t>Didemethylcitalopram$3,4-Dihydroxymandelaldehyde$L-Metanephrine$Demethylcitalopram$Epinine; Deoxyepinephrine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$3-Methoxy-4-hydroxyphenylglycolaldehyde$Dopamine$L-Normetanephrine$5-Hydroxykynurenamine$$3-Methoxy-4-hydroxymandelate; Vanillylmandelic acid$adrenochrome$3-Methoxytyramine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$Indole-3-acetaldehyde$3,4-Dihydroxymandelate$Dopamine 3-O-sulfate</t>
+  </si>
+  <si>
+    <t>C16609,C05577,C05588,C16608,C07453,C09642,C05583,C03758,C05589,C05638,CE2172,C05584,CE5536,C05587,C00788,CE2173,C00637,C05580,C13690</t>
   </si>
   <si>
     <t>(15, 'Tyrosine metabolism');(2, 'Tryptophan metabolism');(2, 'Drug metabolism - cytochrome P450')</t>
@@ -415,7 +415,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.01950741063644289</v>
+        <v>0.015280506439642</v>
       </c>
       <c r="C2">
         <v>51</v>
@@ -435,7 +435,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>0.04511769834350479</v>
+        <v>0.03689150840427854</v>
       </c>
       <c r="C3">
         <v>19</v>

--- a/results/pathways/BC_vs_PC/mcg_modularanalysis_BC_vs_PC.xlsx
+++ b/results/pathways/BC_vs_PC/mcg_modularanalysis_BC_vs_PC.xlsx
@@ -37,25 +37,25 @@
     <t>module_1</t>
   </si>
   <si>
-    <t>5-Phenyl-1,3-oxazinane-2,4-dione$D-Tryptophan$Didemethylcitalopram$4-(2-Aminophenyl)-2,4-dioxobutanoate$3,4-Dihydroxymandelaldehyde$L-Metanephrine$Demethylcitalopram$L-Formylkynurenine$L-Tyrosine$Serotonin$$3-(4-Hydroxyphenyl)pyruvate$Epinine; Deoxyepinephrine$3-O-methyldopa$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$2-Phenyl-1,3-propanediol monocarbamate$3-Methoxy-4-hydroxyphenylglycolaldehyde$L-Tryptophan$Phenylpyruvate$2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$L-Kynurenine$Dopamine$L-Normetanephrine$L-Phenylalanine$5-Hydroxykynurenamine$Homogentisate$Melatonin; N-Acetyl-5-methoxytryptamine$$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$2-Hydroxy-3-(4-hydroxyphenyl)propenoate; 4-Hydroxy-enol-phenylpyruvate$$Dopaquinone$3-Methoxy-4-hydroxymandelate; Vanillylmandelic acid$3-Carbamoyl-2-phenylpropionaldehyde$Formyl-5-hydroxykynurenamine$adrenochrome$3-Methoxytyramine$Formyl-N-acetyl-5-methoxykynurenamine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$Indole-3-acetaldehyde$3-Carbamoyl-2-phenylpropionic acid$6-Hydroxymelatonin$Formylkynurenine$enol-Phenylpyruvate$N-Methylserotonin$3,4-Dihydroxymandelate$N-Acetylserotonin; N-Acetyl-5-hydroxytryptamine$3,4-Dihydroxy-L-phenylalanine$Dopamine 3-O-sulfate$5-Hydroxy-L-tryptophan</t>
-  </si>
-  <si>
-    <t>C16596,C00525,C16609,C01252,C05577,C05588,C16608,C02700,C00082,C00780,CE5860,C01179,C07453,CE2176,C09642,C16586,C05583,C00078,C00166,C05604,C00328,C03758,C05589,C00079,C05638,C00544,C01598,CE3140,C16595,C05350,CE2172,C00822,C05584,C16587,C05647,CE5536,C05587,C05642,C00788,CE2173,C00637,C16591,C05643,C02406,C02763,C06212,C05580,C00978,C00355,C13690,C00643</t>
-  </si>
-  <si>
-    <t>(26, 'Tyrosine metabolism');(18, 'Tryptophan metabolism');(7, 'Drug metabolism - cytochrome P450')</t>
+    <t>L-Metanephrine$3-Carbamoyl-2-phenylpropionic acid$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$5-Hydroxykynurenamine$Dopaquinone$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$5-Hydroxyindoleacetate$3-Methoxy-4-hydroxyphenylglycolaldehyde$Didemethylcitalopram$Serotonin$methyl indole-3-acetate$Indole-3-acetaldehyde$5-Hydroxyindoleacetaldehyde$6,7-Dihydrobiopterin$O2'-4a-cyclic-tetrahydrobiopterin$3,4-Dihydroxymandelate$3-Methoxytyramine$3,4-Dihydroxy-L-phenylalanine$$Dopamine$Formyl-5-hydroxykynurenamine$Phenylpyruvate$Indole-3-acetate$D-Tryptophan$L-Tryptophan$$$5-Phenyl-1,3-oxazinane-2,4-dione$Demethylcitalopram$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$Epinine; Deoxyepinephrine$Homovanillate; Homovanillic acid$3-Methoxy-4-hydroxyphenylacetaldehyde$3-O-methyldopa$adrenochrome$L-Tyrosine$2-Phenyl-1,3-propanediol monocarbamate$Formyl-N-acetyl-5-methoxykynurenamine$5-hydroxytryptophol$enol-Phenylpyruvate$L-Phenylalanine$L-Normetanephrine$quinonoid dihydrobiopterin$3-Carbamoyl-2-phenylpropionaldehyde$3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$3,4-Dihydroxymandelaldehyde$5-Methoxyindoleacetate$5-Hydroxy-L-tryptophan</t>
+  </si>
+  <si>
+    <t>C05588,C16591,C00788,C05638,C00822,C16595,C05635,C05583,C16609,C00780,CE2122,C00637,C05634,C00268,CE5236,C05580,C05587,C00355,CE2172,C03758,C05647,C00166,C00954,C00525,C00078,CE2173,CE5860,C16596,C16608,C09642,C05604,C07453,C05582,C05581,CE2176,CE5536,C00082,C16586,C05642,CE1918,C02763,C00079,C05589,CE2705,C16587,C01161,C05577,C05660,C00643</t>
+  </si>
+  <si>
+    <t>(25, 'Tyrosine metabolism');(16, 'Tryptophan metabolism');(7, 'Drug metabolism - cytochrome P450')</t>
   </si>
   <si>
     <t>module_2</t>
   </si>
   <si>
-    <t>Didemethylcitalopram$3,4-Dihydroxymandelaldehyde$L-Metanephrine$Demethylcitalopram$Epinine; Deoxyepinephrine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$3-Methoxy-4-hydroxyphenylglycolaldehyde$Dopamine$L-Normetanephrine$5-Hydroxykynurenamine$$3-Methoxy-4-hydroxymandelate; Vanillylmandelic acid$adrenochrome$3-Methoxytyramine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$Indole-3-acetaldehyde$3,4-Dihydroxymandelate$Dopamine 3-O-sulfate</t>
-  </si>
-  <si>
-    <t>C16609,C05577,C05588,C16608,C07453,C09642,C05583,C03758,C05589,C05638,CE2172,C05584,CE5536,C05587,C00788,CE2173,C00637,C05580,C13690</t>
-  </si>
-  <si>
-    <t>(15, 'Tyrosine metabolism');(2, 'Tryptophan metabolism');(2, 'Drug metabolism - cytochrome P450')</t>
+    <t>5-hydroxytryptophol$Indole-3-acetaldehyde$Demethylcitalopram$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$5-Hydroxyindoleacetaldehyde$Epinine; Deoxyepinephrine$3-Methoxytyramine$L-Normetanephrine$L-Metanephrine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$5-Hydroxykynurenamine$3-Methoxy-4-hydroxyphenylacetaldehyde$$Dopamine$adrenochrome$$3-Methoxy-4-hydroxyphenylglycolaldehyde$Didemethylcitalopram</t>
+  </si>
+  <si>
+    <t>CE1918,C00637,C16608,C09642,C05634,C07453,C05587,C05589,C05588,C00788,C05638,C05581,CE2172,C03758,CE5536,CE2173,C05583,C16609</t>
+  </si>
+  <si>
+    <t>(12, 'Tyrosine metabolism');(4, 'Tryptophan metabolism');(2, 'Drug metabolism - cytochrome P450')</t>
   </si>
 </sst>
 </file>
@@ -415,10 +415,10 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.015280506439642</v>
+        <v>0.0134925901349259</v>
       </c>
       <c r="C2">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="D2" t="s">
         <v>7</v>
@@ -435,10 +435,10 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>0.03689150840427854</v>
+        <v>0.0152621101526211</v>
       </c>
       <c r="C3">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="D3" t="s">
         <v>11</v>

--- a/results/pathways/BC_vs_PC/mcg_modularanalysis_BC_vs_PC.xlsx
+++ b/results/pathways/BC_vs_PC/mcg_modularanalysis_BC_vs_PC.xlsx
@@ -37,10 +37,10 @@
     <t>module_1</t>
   </si>
   <si>
-    <t>L-Metanephrine$3-Carbamoyl-2-phenylpropionic acid$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$5-Hydroxykynurenamine$Dopaquinone$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$5-Hydroxyindoleacetate$3-Methoxy-4-hydroxyphenylglycolaldehyde$Didemethylcitalopram$Serotonin$methyl indole-3-acetate$Indole-3-acetaldehyde$5-Hydroxyindoleacetaldehyde$6,7-Dihydrobiopterin$O2'-4a-cyclic-tetrahydrobiopterin$3,4-Dihydroxymandelate$3-Methoxytyramine$3,4-Dihydroxy-L-phenylalanine$$Dopamine$Formyl-5-hydroxykynurenamine$Phenylpyruvate$Indole-3-acetate$D-Tryptophan$L-Tryptophan$$$5-Phenyl-1,3-oxazinane-2,4-dione$Demethylcitalopram$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$Epinine; Deoxyepinephrine$Homovanillate; Homovanillic acid$3-Methoxy-4-hydroxyphenylacetaldehyde$3-O-methyldopa$adrenochrome$L-Tyrosine$2-Phenyl-1,3-propanediol monocarbamate$Formyl-N-acetyl-5-methoxykynurenamine$5-hydroxytryptophol$enol-Phenylpyruvate$L-Phenylalanine$L-Normetanephrine$quinonoid dihydrobiopterin$3-Carbamoyl-2-phenylpropionaldehyde$3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$3,4-Dihydroxymandelaldehyde$5-Methoxyindoleacetate$5-Hydroxy-L-tryptophan</t>
-  </si>
-  <si>
-    <t>C05588,C16591,C00788,C05638,C00822,C16595,C05635,C05583,C16609,C00780,CE2122,C00637,C05634,C00268,CE5236,C05580,C05587,C00355,CE2172,C03758,C05647,C00166,C00954,C00525,C00078,CE2173,CE5860,C16596,C16608,C09642,C05604,C07453,C05582,C05581,CE2176,CE5536,C00082,C16586,C05642,CE1918,C02763,C00079,C05589,CE2705,C16587,C01161,C05577,C05660,C00643</t>
+    <t>5-Methoxyindoleacetate$5-Hydroxyindoleacetate$2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$3-O-methyldopa$L-Normetanephrine$3,4-Dihydroxy-L-phenylalanine$3-Methoxy-4-hydroxyphenylglycolaldehyde$6,7-Dihydrobiopterin$3,4-Dihydroxymandelate$Epinine; Deoxyepinephrine$3-Methoxytyramine$Didemethylcitalopram$5-hydroxytryptophol$Formyl-N-acetyl-5-methoxykynurenamine$3-Methoxy-4-hydroxyphenylacetaldehyde$$Dopamine$5-Hydroxykynurenamine$L-Metanephrine$2-Phenyl-1,3-propanediol monocarbamate$Demethylcitalopram$3,4-Dihydroxymandelaldehyde$5-Hydroxyindoleacetaldehyde$Indole-3-acetate$L-Tyrosine$Serotonin$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$5-Phenyl-1,3-oxazinane-2,4-dione$O2'-4a-cyclic-tetrahydrobiopterin$Phenylpyruvate$Indole-3-acetaldehyde$D-Tryptophan$Homovanillate; Homovanillic acid$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$Formyl-5-hydroxykynurenamine$enol-Phenylpyruvate$$3-Carbamoyl-2-phenylpropionaldehyde$3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$5-Hydroxy-L-tryptophan$adrenochrome$L-Tryptophan$$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$methyl indole-3-acetate$quinonoid dihydrobiopterin$Dopaquinone$3-Carbamoyl-2-phenylpropionic acid$L-Phenylalanine</t>
+  </si>
+  <si>
+    <t>C05660,C05635,C05604,CE2176,C05589,C00355,C05583,C00268,C05580,C07453,C05587,C16609,CE1918,C05642,C05581,CE2173,C03758,C05638,C05588,C16586,C16608,C05577,C05634,C00954,C00082,C00780,C09642,C16596,CE5236,C00166,C00637,C00525,C05582,C00788,C05647,C02763,CE5860,C16587,C01161,C00643,CE5536,C00078,CE2172,C16595,CE2122,CE2705,C00822,C16591,C00079</t>
   </si>
   <si>
     <t>(25, 'Tyrosine metabolism');(16, 'Tryptophan metabolism');(7, 'Drug metabolism - cytochrome P450')</t>
@@ -49,10 +49,10 @@
     <t>module_2</t>
   </si>
   <si>
-    <t>5-hydroxytryptophol$Indole-3-acetaldehyde$Demethylcitalopram$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$5-Hydroxyindoleacetaldehyde$Epinine; Deoxyepinephrine$3-Methoxytyramine$L-Normetanephrine$L-Metanephrine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$5-Hydroxykynurenamine$3-Methoxy-4-hydroxyphenylacetaldehyde$$Dopamine$adrenochrome$$3-Methoxy-4-hydroxyphenylglycolaldehyde$Didemethylcitalopram</t>
-  </si>
-  <si>
-    <t>CE1918,C00637,C16608,C09642,C05634,C07453,C05587,C05589,C05588,C00788,C05638,C05581,CE2172,C03758,CE5536,CE2173,C05583,C16609</t>
+    <t>5-hydroxytryptophol$adrenochrome$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$3-Methoxy-4-hydroxyphenylacetaldehyde$$Dopamine$$L-Normetanephrine$Demethylcitalopram$5-Hydroxykynurenamine$Indole-3-acetaldehyde$L-Metanephrine$3-Methoxy-4-hydroxyphenylglycolaldehyde$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$Epinine; Deoxyepinephrine$3-Methoxytyramine$5-Hydroxyindoleacetaldehyde$Didemethylcitalopram</t>
+  </si>
+  <si>
+    <t>CE1918,CE5536,C09642,C05581,CE2172,C03758,CE2173,C05589,C16608,C05638,C00637,C05588,C05583,C00788,C07453,C05587,C05634,C16609</t>
   </si>
   <si>
     <t>(12, 'Tyrosine metabolism');(4, 'Tryptophan metabolism');(2, 'Drug metabolism - cytochrome P450')</t>
@@ -415,7 +415,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.0134925901349259</v>
+        <v>0.01542416452442159</v>
       </c>
       <c r="C2">
         <v>49</v>
@@ -435,7 +435,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>0.0152621101526211</v>
+        <v>0.01735218508997429</v>
       </c>
       <c r="C3">
         <v>18</v>

--- a/results/pathways/BC_vs_PC/mcg_modularanalysis_BC_vs_PC.xlsx
+++ b/results/pathways/BC_vs_PC/mcg_modularanalysis_BC_vs_PC.xlsx
@@ -37,10 +37,10 @@
     <t>module_1</t>
   </si>
   <si>
-    <t>5-Methoxyindoleacetate$5-Hydroxyindoleacetate$2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$3-O-methyldopa$L-Normetanephrine$3,4-Dihydroxy-L-phenylalanine$3-Methoxy-4-hydroxyphenylglycolaldehyde$6,7-Dihydrobiopterin$3,4-Dihydroxymandelate$Epinine; Deoxyepinephrine$3-Methoxytyramine$Didemethylcitalopram$5-hydroxytryptophol$Formyl-N-acetyl-5-methoxykynurenamine$3-Methoxy-4-hydroxyphenylacetaldehyde$$Dopamine$5-Hydroxykynurenamine$L-Metanephrine$2-Phenyl-1,3-propanediol monocarbamate$Demethylcitalopram$3,4-Dihydroxymandelaldehyde$5-Hydroxyindoleacetaldehyde$Indole-3-acetate$L-Tyrosine$Serotonin$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$5-Phenyl-1,3-oxazinane-2,4-dione$O2'-4a-cyclic-tetrahydrobiopterin$Phenylpyruvate$Indole-3-acetaldehyde$D-Tryptophan$Homovanillate; Homovanillic acid$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$Formyl-5-hydroxykynurenamine$enol-Phenylpyruvate$$3-Carbamoyl-2-phenylpropionaldehyde$3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$5-Hydroxy-L-tryptophan$adrenochrome$L-Tryptophan$$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$methyl indole-3-acetate$quinonoid dihydrobiopterin$Dopaquinone$3-Carbamoyl-2-phenylpropionic acid$L-Phenylalanine</t>
-  </si>
-  <si>
-    <t>C05660,C05635,C05604,CE2176,C05589,C00355,C05583,C00268,C05580,C07453,C05587,C16609,CE1918,C05642,C05581,CE2173,C03758,C05638,C05588,C16586,C16608,C05577,C05634,C00954,C00082,C00780,C09642,C16596,CE5236,C00166,C00637,C00525,C05582,C00788,C05647,C02763,CE5860,C16587,C01161,C00643,CE5536,C00078,CE2172,C16595,CE2122,CE2705,C00822,C16591,C00079</t>
+    <t>L-Metanephrine$Formyl-N-acetyl-5-methoxykynurenamine$5-Phenyl-1,3-oxazinane-2,4-dione$3-O-methyldopa$quinonoid dihydrobiopterin$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$L-Normetanephrine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$3,4-Dihydroxymandelaldehyde$3-Methoxy-4-hydroxyphenylacetaldehyde$2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$5-hydroxytryptophol$L-Tryptophan$Epinine; Deoxyepinephrine$enol-Phenylpyruvate$Indole-3-acetate$Indole-3-acetaldehyde$3-Methoxytyramine$$Formyl-5-hydroxykynurenamine$L-Phenylalanine$3,4-Dihydroxymandelate$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$5-Hydroxykynurenamine$adrenochrome$5-Hydroxy-L-tryptophan$Phenylpyruvate$D-Tryptophan$3-Carbamoyl-2-phenylpropionic acid$Dopaquinone$3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$$5-Hydroxyindoleacetate$O2'-4a-cyclic-tetrahydrobiopterin$6,7-Dihydrobiopterin$L-Tyrosine$3-Carbamoyl-2-phenylpropionaldehyde$Homovanillate; Homovanillic acid$5-Hydroxyindoleacetaldehyde$Serotonin$Demethylcitalopram$Didemethylcitalopram$3,4-Dihydroxy-L-phenylalanine$3-Methoxy-4-hydroxyphenylglycolaldehyde$Dopamine$5-Methoxyindoleacetate$2-Phenyl-1,3-propanediol monocarbamate$methyl indole-3-acetate</t>
+  </si>
+  <si>
+    <t>C05588,C05642,C16596,CE2176,CE2705,C16595,C05589,C00788,CE2173,C05577,C05581,C05604,CE1918,C00078,C07453,C02763,C00954,C00637,C05587,CE5860,C05647,C00079,C05580,C09642,C05638,CE5536,C00643,C00166,C00525,C16591,C00822,C01161,CE2172,C05635,CE5236,C00268,C00082,C16587,C05582,C05634,C00780,C16608,C16609,C00355,C05583,C03758,C05660,C16586,CE2122</t>
   </si>
   <si>
     <t>(25, 'Tyrosine metabolism');(16, 'Tryptophan metabolism');(7, 'Drug metabolism - cytochrome P450')</t>
@@ -49,10 +49,10 @@
     <t>module_2</t>
   </si>
   <si>
-    <t>5-hydroxytryptophol$adrenochrome$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$3-Methoxy-4-hydroxyphenylacetaldehyde$$Dopamine$$L-Normetanephrine$Demethylcitalopram$5-Hydroxykynurenamine$Indole-3-acetaldehyde$L-Metanephrine$3-Methoxy-4-hydroxyphenylglycolaldehyde$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$Epinine; Deoxyepinephrine$3-Methoxytyramine$5-Hydroxyindoleacetaldehyde$Didemethylcitalopram</t>
-  </si>
-  <si>
-    <t>CE1918,CE5536,C09642,C05581,CE2172,C03758,CE2173,C05589,C16608,C05638,C00637,C05588,C05583,C00788,C07453,C05587,C05634,C16609</t>
+    <t>L-Metanephrine$adrenochrome$5-Hydroxyindoleacetaldehyde$Indole-3-acetaldehyde$5-hydroxytryptophol$3-Methoxytyramine$Demethylcitalopram$$Didemethylcitalopram$L-Normetanephrine$3-Methoxy-4-hydroxyphenylglycolaldehyde$Dopamine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$3-Methoxy-4-hydroxyphenylacetaldehyde$5-Hydroxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$Epinine; Deoxyepinephrine</t>
+  </si>
+  <si>
+    <t>C05588,CE5536,C05634,C00637,CE1918,C05587,C16608,CE2172,C16609,C05589,C05583,C03758,C00788,CE2173,C05581,C05638,C09642,C07453</t>
   </si>
   <si>
     <t>(12, 'Tyrosine metabolism');(4, 'Tryptophan metabolism');(2, 'Drug metabolism - cytochrome P450')</t>
@@ -415,7 +415,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.01542416452442159</v>
+        <v>0.01513821851689337</v>
       </c>
       <c r="C2">
         <v>49</v>
@@ -435,7 +435,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>0.01735218508997429</v>
+        <v>0.01733216322948662</v>
       </c>
       <c r="C3">
         <v>18</v>

--- a/results/pathways/BC_vs_PC/mcg_modularanalysis_BC_vs_PC.xlsx
+++ b/results/pathways/BC_vs_PC/mcg_modularanalysis_BC_vs_PC.xlsx
@@ -37,10 +37,10 @@
     <t>module_1</t>
   </si>
   <si>
-    <t>L-Metanephrine$Formyl-N-acetyl-5-methoxykynurenamine$5-Phenyl-1,3-oxazinane-2,4-dione$3-O-methyldopa$quinonoid dihydrobiopterin$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$L-Normetanephrine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$3,4-Dihydroxymandelaldehyde$3-Methoxy-4-hydroxyphenylacetaldehyde$2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$5-hydroxytryptophol$L-Tryptophan$Epinine; Deoxyepinephrine$enol-Phenylpyruvate$Indole-3-acetate$Indole-3-acetaldehyde$3-Methoxytyramine$$Formyl-5-hydroxykynurenamine$L-Phenylalanine$3,4-Dihydroxymandelate$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$5-Hydroxykynurenamine$adrenochrome$5-Hydroxy-L-tryptophan$Phenylpyruvate$D-Tryptophan$3-Carbamoyl-2-phenylpropionic acid$Dopaquinone$3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$$5-Hydroxyindoleacetate$O2'-4a-cyclic-tetrahydrobiopterin$6,7-Dihydrobiopterin$L-Tyrosine$3-Carbamoyl-2-phenylpropionaldehyde$Homovanillate; Homovanillic acid$5-Hydroxyindoleacetaldehyde$Serotonin$Demethylcitalopram$Didemethylcitalopram$3,4-Dihydroxy-L-phenylalanine$3-Methoxy-4-hydroxyphenylglycolaldehyde$Dopamine$5-Methoxyindoleacetate$2-Phenyl-1,3-propanediol monocarbamate$methyl indole-3-acetate</t>
-  </si>
-  <si>
-    <t>C05588,C05642,C16596,CE2176,CE2705,C16595,C05589,C00788,CE2173,C05577,C05581,C05604,CE1918,C00078,C07453,C02763,C00954,C00637,C05587,CE5860,C05647,C00079,C05580,C09642,C05638,CE5536,C00643,C00166,C00525,C16591,C00822,C01161,CE2172,C05635,CE5236,C00268,C00082,C16587,C05582,C05634,C00780,C16608,C16609,C00355,C05583,C03758,C05660,C16586,CE2122</t>
+    <t>3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$L-Phenylalanine$Indole-3-acetate$Dopaquinone$5-hydroxytryptophol$Homovanillate; Homovanillic acid$5-Phenyl-1,3-oxazinane-2,4-dione$3-Carbamoyl-2-phenylpropionaldehyde$Dopamine$5-Hydroxykynurenamine$L-Metanephrine$3-Carbamoyl-2-phenylpropionic acid$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$3-Methoxy-4-hydroxyphenylglycolaldehyde$L-Tyrosine$quinonoid dihydrobiopterin$L-Tryptophan$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$6,7-Dihydrobiopterin$3-Methoxy-4-hydroxyphenylacetaldehyde$Demethylcitalopram$5-Methoxyindoleacetate$Formyl-N-acetyl-5-methoxykynurenamine$3,4-Dihydroxymandelate$$L-Normetanephrine$2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$5-Hydroxyindoleacetaldehyde$D-Tryptophan$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$Serotonin$O2'-4a-cyclic-tetrahydrobiopterin$methyl indole-3-acetate$3,4-Dihydroxy-L-phenylalanine$$enol-Phenylpyruvate$Phenylpyruvate$adrenochrome$Epinine; Deoxyepinephrine$Didemethylcitalopram$Formyl-5-hydroxykynurenamine$Indole-3-acetaldehyde$5-Hydroxyindoleacetate$3,4-Dihydroxymandelaldehyde$5-Hydroxy-L-tryptophan$3-O-methyldopa$2-Phenyl-1,3-propanediol monocarbamate$$3-Methoxytyramine</t>
+  </si>
+  <si>
+    <t>C01161,C00079,C00954,C00822,CE1918,C05582,C16596,C16587,C03758,C05638,C05588,C16591,C00788,C05583,C00082,CE2705,C00078,C16595,C00268,C05581,C16608,C05660,C05642,C05580,CE2173,C05589,C05604,C05634,C00525,C09642,C00780,CE5236,CE2122,C00355,CE2172,C02763,C00166,CE5536,C07453,C16609,C05647,C00637,C05635,C05577,C00643,CE2176,C16586,CE5860,C05587</t>
   </si>
   <si>
     <t>(25, 'Tyrosine metabolism');(16, 'Tryptophan metabolism');(7, 'Drug metabolism - cytochrome P450')</t>
@@ -49,10 +49,10 @@
     <t>module_2</t>
   </si>
   <si>
-    <t>L-Metanephrine$adrenochrome$5-Hydroxyindoleacetaldehyde$Indole-3-acetaldehyde$5-hydroxytryptophol$3-Methoxytyramine$Demethylcitalopram$$Didemethylcitalopram$L-Normetanephrine$3-Methoxy-4-hydroxyphenylglycolaldehyde$Dopamine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$3-Methoxy-4-hydroxyphenylacetaldehyde$5-Hydroxykynurenamine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$Epinine; Deoxyepinephrine</t>
-  </si>
-  <si>
-    <t>C05588,CE5536,C05634,C00637,CE1918,C05587,C16608,CE2172,C16609,C05589,C05583,C03758,C00788,CE2173,C05581,C05638,C09642,C07453</t>
+    <t>adrenochrome$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$3-Methoxy-4-hydroxyphenylglycolaldehyde$Epinine; Deoxyepinephrine$L-Normetanephrine$Didemethylcitalopram$Indole-3-acetaldehyde$5-Hydroxyindoleacetaldehyde$5-hydroxytryptophol$3-Methoxytyramine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$3-Methoxy-4-hydroxyphenylacetaldehyde$5-Hydroxykynurenamine$Demethylcitalopram$Dopamine$$L-Metanephrine</t>
+  </si>
+  <si>
+    <t>CE5536,C00788,CE2173,C05583,C07453,C05589,C16609,C00637,C05634,CE1918,C05587,C09642,C05581,C05638,C16608,C03758,CE2172,C05588</t>
   </si>
   <si>
     <t>(12, 'Tyrosine metabolism');(4, 'Tryptophan metabolism');(2, 'Drug metabolism - cytochrome P450')</t>
@@ -415,7 +415,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.01513821851689337</v>
+        <v>0.0126942438170278</v>
       </c>
       <c r="C2">
         <v>49</v>
@@ -435,7 +435,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>0.01733216322948662</v>
+        <v>0.01400744145327205</v>
       </c>
       <c r="C3">
         <v>18</v>

--- a/results/pathways/BC_vs_PC/mcg_modularanalysis_BC_vs_PC.xlsx
+++ b/results/pathways/BC_vs_PC/mcg_modularanalysis_BC_vs_PC.xlsx
@@ -37,10 +37,10 @@
     <t>module_1</t>
   </si>
   <si>
-    <t>3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$L-Phenylalanine$Indole-3-acetate$Dopaquinone$5-hydroxytryptophol$Homovanillate; Homovanillic acid$5-Phenyl-1,3-oxazinane-2,4-dione$3-Carbamoyl-2-phenylpropionaldehyde$Dopamine$5-Hydroxykynurenamine$L-Metanephrine$3-Carbamoyl-2-phenylpropionic acid$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$3-Methoxy-4-hydroxyphenylglycolaldehyde$L-Tyrosine$quinonoid dihydrobiopterin$L-Tryptophan$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$6,7-Dihydrobiopterin$3-Methoxy-4-hydroxyphenylacetaldehyde$Demethylcitalopram$5-Methoxyindoleacetate$Formyl-N-acetyl-5-methoxykynurenamine$3,4-Dihydroxymandelate$$L-Normetanephrine$2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$5-Hydroxyindoleacetaldehyde$D-Tryptophan$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$Serotonin$O2'-4a-cyclic-tetrahydrobiopterin$methyl indole-3-acetate$3,4-Dihydroxy-L-phenylalanine$$enol-Phenylpyruvate$Phenylpyruvate$adrenochrome$Epinine; Deoxyepinephrine$Didemethylcitalopram$Formyl-5-hydroxykynurenamine$Indole-3-acetaldehyde$5-Hydroxyindoleacetate$3,4-Dihydroxymandelaldehyde$5-Hydroxy-L-tryptophan$3-O-methyldopa$2-Phenyl-1,3-propanediol monocarbamate$$3-Methoxytyramine</t>
-  </si>
-  <si>
-    <t>C01161,C00079,C00954,C00822,CE1918,C05582,C16596,C16587,C03758,C05638,C05588,C16591,C00788,C05583,C00082,CE2705,C00078,C16595,C00268,C05581,C16608,C05660,C05642,C05580,CE2173,C05589,C05604,C05634,C00525,C09642,C00780,CE5236,CE2122,C00355,CE2172,C02763,C00166,CE5536,C07453,C16609,C05647,C00637,C05635,C05577,C00643,CE2176,C16586,CE5860,C05587</t>
+    <t>2-Phenyl-1,3-propanediol monocarbamate$5-Hydroxyindoleacetaldehyde$Epinine; Deoxyepinephrine$Homovanillate; Homovanillic acid$5-Hydroxy-L-tryptophan$enol-Phenylpyruvate$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$$methyl indole-3-acetate$3-Methoxy-4-hydroxyphenylacetaldehyde$L-Tryptophan$3,4-Dihydroxymandelate$5-hydroxytryptophol$Formyl-5-hydroxykynurenamine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$5-Hydroxyindoleacetate$5-Hydroxykynurenamine$3,4-Dihydroxy-L-phenylalanine$$Dopaquinone$quinonoid dihydrobiopterin$Serotonin$5-Methoxyindoleacetate$Phenylpyruvate$5-Phenyl-1,3-oxazinane-2,4-dione$Indole-3-acetaldehyde$O2'-4a-cyclic-tetrahydrobiopterin$Dopamine$Didemethylcitalopram$3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$3-Carbamoyl-2-phenylpropionaldehyde$3-Methoxy-4-hydroxyphenylglycolaldehyde$L-Normetanephrine$adrenochrome$2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$3-Carbamoyl-2-phenylpropionic acid$L-Phenylalanine$Demethylcitalopram$Formyl-N-acetyl-5-methoxykynurenamine$L-Tyrosine$L-Metanephrine$$3,4-Dihydroxymandelaldehyde$3-Methoxytyramine$6,7-Dihydrobiopterin$3-O-methyldopa$Indole-3-acetate$D-Tryptophan</t>
+  </si>
+  <si>
+    <t>C16586,C05634,C07453,C05582,C00643,C02763,C16595,CE2173,CE2122,C05581,C00078,C05580,CE1918,C05647,C00788,C05635,C05638,C00355,CE5860,C00822,CE2705,C00780,C05660,C00166,C16596,C00637,CE5236,C03758,C16609,C01161,C16587,C05583,C05589,CE5536,C05604,C09642,C16591,C00079,C16608,C05642,C00082,C05588,CE2172,C05577,C05587,C00268,CE2176,C00954,C00525</t>
   </si>
   <si>
     <t>(25, 'Tyrosine metabolism');(16, 'Tryptophan metabolism');(7, 'Drug metabolism - cytochrome P450')</t>
@@ -49,10 +49,10 @@
     <t>module_2</t>
   </si>
   <si>
-    <t>adrenochrome$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$$3-Methoxy-4-hydroxyphenylglycolaldehyde$Epinine; Deoxyepinephrine$L-Normetanephrine$Didemethylcitalopram$Indole-3-acetaldehyde$5-Hydroxyindoleacetaldehyde$5-hydroxytryptophol$3-Methoxytyramine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$3-Methoxy-4-hydroxyphenylacetaldehyde$5-Hydroxykynurenamine$Demethylcitalopram$Dopamine$$L-Metanephrine</t>
-  </si>
-  <si>
-    <t>CE5536,C00788,CE2173,C05583,C07453,C05589,C16609,C00637,C05634,CE1918,C05587,C09642,C05581,C05638,C16608,C03758,CE2172,C05588</t>
+    <t>Demethylcitalopram$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$5-Hydroxyindoleacetaldehyde$Indole-3-acetaldehyde$Epinine; Deoxyepinephrine$Dopamine$Didemethylcitalopram$L-Metanephrine$5-Hydroxykynurenamine$$3-Methoxy-4-hydroxyphenylglycolaldehyde$L-Normetanephrine$$3-Methoxytyramine$adrenochrome$3-Methoxy-4-hydroxyphenylacetaldehyde$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$5-hydroxytryptophol</t>
+  </si>
+  <si>
+    <t>C16608,C00788,C05634,C00637,C07453,C03758,C16609,C05588,C05638,CE2172,C05583,C05589,CE2173,C05587,CE5536,C05581,C09642,CE1918</t>
   </si>
   <si>
     <t>(12, 'Tyrosine metabolism');(4, 'Tryptophan metabolism');(2, 'Drug metabolism - cytochrome P450')</t>
@@ -415,7 +415,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.0126942438170278</v>
+        <v>0.01244184788488586</v>
       </c>
       <c r="C2">
         <v>49</v>
@@ -435,7 +435,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>0.01400744145327205</v>
+        <v>0.01449745753543222</v>
       </c>
       <c r="C3">
         <v>18</v>

--- a/results/pathways/BC_vs_PC/mcg_modularanalysis_BC_vs_PC.xlsx
+++ b/results/pathways/BC_vs_PC/mcg_modularanalysis_BC_vs_PC.xlsx
@@ -37,10 +37,10 @@
     <t>module_1</t>
   </si>
   <si>
-    <t>2-Phenyl-1,3-propanediol monocarbamate$5-Hydroxyindoleacetaldehyde$Epinine; Deoxyepinephrine$Homovanillate; Homovanillic acid$5-Hydroxy-L-tryptophan$enol-Phenylpyruvate$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$$methyl indole-3-acetate$3-Methoxy-4-hydroxyphenylacetaldehyde$L-Tryptophan$3,4-Dihydroxymandelate$5-hydroxytryptophol$Formyl-5-hydroxykynurenamine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$5-Hydroxyindoleacetate$5-Hydroxykynurenamine$3,4-Dihydroxy-L-phenylalanine$$Dopaquinone$quinonoid dihydrobiopterin$Serotonin$5-Methoxyindoleacetate$Phenylpyruvate$5-Phenyl-1,3-oxazinane-2,4-dione$Indole-3-acetaldehyde$O2'-4a-cyclic-tetrahydrobiopterin$Dopamine$Didemethylcitalopram$3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$3-Carbamoyl-2-phenylpropionaldehyde$3-Methoxy-4-hydroxyphenylglycolaldehyde$L-Normetanephrine$adrenochrome$2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$3-Carbamoyl-2-phenylpropionic acid$L-Phenylalanine$Demethylcitalopram$Formyl-N-acetyl-5-methoxykynurenamine$L-Tyrosine$L-Metanephrine$$3,4-Dihydroxymandelaldehyde$3-Methoxytyramine$6,7-Dihydrobiopterin$3-O-methyldopa$Indole-3-acetate$D-Tryptophan</t>
-  </si>
-  <si>
-    <t>C16586,C05634,C07453,C05582,C00643,C02763,C16595,CE2173,CE2122,C05581,C00078,C05580,CE1918,C05647,C00788,C05635,C05638,C00355,CE5860,C00822,CE2705,C00780,C05660,C00166,C16596,C00637,CE5236,C03758,C16609,C01161,C16587,C05583,C05589,CE5536,C05604,C09642,C16591,C00079,C16608,C05642,C00082,C05588,CE2172,C05577,C05587,C00268,CE2176,C00954,C00525</t>
+    <t>3-Carbamoyl-2-phenylpropionaldehyde$$Formyl-5-hydroxykynurenamine$5-Hydroxyindoleacetaldehyde$6,7-Dihydrobiopterin$enol-Phenylpyruvate$Epinine; Deoxyepinephrine$L-Tryptophan$Homovanillate; Homovanillic acid$3-Methoxytyramine$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$3,4-Dihydroxy-L-phenylalanine$L-Tyrosine$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$Indole-3-acetate$3,4-Dihydroxyphenylacetate; 3,4-Dihydroxyphenylacetic acid; 3,4-Dihydroxyphenyl acetate; 3,4-Dihydroxyphenyl acetic acid; Homoprotocatechuate$3,4-Dihydroxymandelaldehyde$adrenochrome$$quinonoid dihydrobiopterin$3-Methoxy-4-hydroxyphenylglycolaldehyde$O2'-4a-cyclic-tetrahydrobiopterin$Dopamine$2-Carboxy-2,3-dihydro-5,6-dihydroxyindole; Leucodopachrome$Serotonin$L-Normetanephrine$3,4-Dihydroxymandelate$5-Phenyl-1,3-oxazinane-2,4-dione$3-O-methyldopa$5-Hydroxykynurenamine$5-Hydroxyindoleacetate$methyl indole-3-acetate$Phenylpyruvate$3-Carbamoyl-2-phenylpropionic acid$Indole-3-acetaldehyde$Didemethylcitalopram$L-Metanephrine$5-Hydroxy-L-tryptophan$Formyl-N-acetyl-5-methoxykynurenamine$5-Methoxyindoleacetate$5-hydroxytryptophol$Demethylcitalopram$L-Phenylalanine$3-Methoxy-4-hydroxyphenylacetaldehyde$4-Hydroxy-5-phenyltetrahydro-1,3-oxazin-2-one$2-Phenyl-1,3-propanediol monocarbamate$D-Tryptophan$Dopaquinone$</t>
+  </si>
+  <si>
+    <t>C16587,CE2172,C05647,C05634,C00268,C02763,C07453,C00078,C05582,C05587,C00788,C00355,C00082,C09642,C00954,C01161,C05577,CE5536,CE2173,CE2705,C05583,CE5236,C03758,C05604,C00780,C05589,C05580,C16596,CE2176,C05638,C05635,CE2122,C00166,C16591,C00637,C16609,C05588,C00643,C05642,C05660,CE1918,C16608,C00079,C05581,C16595,C16586,C00525,C00822,CE5860</t>
   </si>
   <si>
     <t>(25, 'Tyrosine metabolism');(16, 'Tryptophan metabolism');(7, 'Drug metabolism - cytochrome P450')</t>
@@ -49,10 +49,10 @@
     <t>module_2</t>
   </si>
   <si>
-    <t>Demethylcitalopram$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol$5-Hydroxyindoleacetaldehyde$Indole-3-acetaldehyde$Epinine; Deoxyepinephrine$Dopamine$Didemethylcitalopram$L-Metanephrine$5-Hydroxykynurenamine$$3-Methoxy-4-hydroxyphenylglycolaldehyde$L-Normetanephrine$$3-Methoxytyramine$adrenochrome$3-Methoxy-4-hydroxyphenylacetaldehyde$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$5-hydroxytryptophol</t>
-  </si>
-  <si>
-    <t>C16608,C00788,C05634,C00637,C07453,C03758,C16609,C05588,C05638,CE2172,C05583,C05589,CE2173,C05587,CE5536,C05581,C09642,CE1918</t>
+    <t>3-Methoxy-4-hydroxyphenylacetaldehyde$L-Normetanephrine$$(-)-Salsolinol; 6,7-Isoquinolinediol, 1,2,3,4-tetrahydro-1-methyl-, (S)-; Salsolinol$5-Hydroxyindoleacetaldehyde$5-Hydroxykynurenamine$adrenochrome$$Epinine; Deoxyepinephrine$Indole-3-acetaldehyde$Didemethylcitalopram$L-Metanephrine$3-Methoxy-4-hydroxyphenylglycolaldehyde$5-hydroxytryptophol$3-Methoxytyramine$Dopamine$Demethylcitalopram$L-Adrenaline; (R)-(-)-Adrenaline; (R)-(-)-Epinephrine; (R)-(-)-Epirenamine; (R)-(-)-Adnephrine; 4-[(1R)-1-Hydroxy-2-(methylamino)ethyl]-1,2-benzenediol</t>
+  </si>
+  <si>
+    <t>C05581,C05589,CE2172,C09642,C05634,C05638,CE5536,CE2173,C07453,C00637,C16609,C05588,C05583,CE1918,C05587,C03758,C16608,C00788</t>
   </si>
   <si>
     <t>(12, 'Tyrosine metabolism');(4, 'Tryptophan metabolism');(2, 'Drug metabolism - cytochrome P450')</t>
@@ -415,7 +415,7 @@
         <v>6</v>
       </c>
       <c r="B2">
-        <v>0.01244184788488586</v>
+        <v>0.01189110253468238</v>
       </c>
       <c r="C2">
         <v>49</v>
@@ -435,7 +435,7 @@
         <v>10</v>
       </c>
       <c r="B3">
-        <v>0.01449745753543222</v>
+        <v>0.01335141337227496</v>
       </c>
       <c r="C3">
         <v>18</v>
